--- a/MinMax/scripts/comparison/violations_comparison_table_118_100.xlsx
+++ b/MinMax/scripts/comparison/violations_comparison_table_118_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Pg Vm Model False</t>
   </si>
@@ -31,22 +31,40 @@
     <t>Violation Metric</t>
   </si>
   <si>
-    <t>Pg Avg Violation</t>
-  </si>
-  <si>
-    <t>Pg Max Violation</t>
-  </si>
-  <si>
-    <t>Qg Avg Violation</t>
-  </si>
-  <si>
-    <t>Qg Max Violation</t>
-  </si>
-  <si>
-    <t>Vm Avg Violation</t>
-  </si>
-  <si>
-    <t>Vm Max Violation</t>
+    <t>Pg up Avg Violation</t>
+  </si>
+  <si>
+    <t>Pg up Max Violation</t>
+  </si>
+  <si>
+    <t>Pg down Avg Violation</t>
+  </si>
+  <si>
+    <t>Pg down Max Violation</t>
+  </si>
+  <si>
+    <t>Qg up Avg Violation</t>
+  </si>
+  <si>
+    <t>Qg up Max Violation</t>
+  </si>
+  <si>
+    <t>Qg down Avg Violation</t>
+  </si>
+  <si>
+    <t>Qg down Max Violation</t>
+  </si>
+  <si>
+    <t>Vm up Avg Violation</t>
+  </si>
+  <si>
+    <t>Vm up Max Violation</t>
+  </si>
+  <si>
+    <t>Vm down Avg Violation</t>
+  </si>
+  <si>
+    <t>Vm down Max Violation</t>
   </si>
   <si>
     <t>Ibr Avg Violation</t>
@@ -416,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -475,16 +493,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>6.460986332967877E-05</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.0001794837153283879</v>
       </c>
       <c r="D4">
-        <v>0.004053681623190641</v>
+        <v>0.009775315411388874</v>
       </c>
       <c r="E4">
-        <v>0.002465138677507639</v>
+        <v>0.009787281043827534</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -492,16 +510,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.01488589867949486</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>0.1024265214800835</v>
       </c>
       <c r="D5">
-        <v>0.4303729832172394</v>
+        <v>0.4259120225906372</v>
       </c>
       <c r="E5">
-        <v>0.5581697225570679</v>
+        <v>0.2000734806060791</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -509,16 +527,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.0001610807958059013</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0.0001610869803698733</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>4.741498855764803E-07</v>
+        <v>0.004053681623190641</v>
       </c>
       <c r="E6">
-        <v>2.067854802589864E-05</v>
+        <v>0.002465138677507639</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -526,16 +544,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>0.01920199394226074</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.01920586824417114</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0.004324555397033691</v>
+        <v>0.4303729832172394</v>
       </c>
       <c r="E7">
-        <v>0.01223862171173096</v>
+        <v>0.5581697225570679</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -543,16 +561,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.1711654365062714</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0.1711642146110535</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.002058504614979029</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>0.002076153177767992</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -560,16 +578,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>8.231096267700195</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>8.231952667236328</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.1476129293441772</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>0.1197323873639107</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -577,16 +595,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>6.320630931512637E-08</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>6.146482684925767E-08</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>2.002440429105544E-06</v>
+        <v>4.741498855764803E-07</v>
       </c>
       <c r="E10">
-        <v>1.988179615877243E-06</v>
+        <v>2.067854802589864E-05</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -594,15 +612,117 @@
         <v>14</v>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0.004324555397033691</v>
+      </c>
+      <c r="E11">
+        <v>0.01223862171173096</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>0.0001610807958059013</v>
+      </c>
+      <c r="C12">
+        <v>0.0001610869803698733</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>0.01920199394226074</v>
+      </c>
+      <c r="C13">
+        <v>0.01920586824417114</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>0.1711654365062714</v>
+      </c>
+      <c r="C14">
+        <v>0.1711642146110535</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>8.231096267700195</v>
+      </c>
+      <c r="C15">
+        <v>8.231952667236328</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <v>6.320630931512637E-08</v>
+      </c>
+      <c r="C16">
+        <v>6.146482684925767E-08</v>
+      </c>
+      <c r="D16">
+        <v>2.002440429105544E-06</v>
+      </c>
+      <c r="E16">
+        <v>1.988179615877243E-06</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17">
         <v>3.659044569649694E-06</v>
       </c>
-      <c r="C11">
+      <c r="C17">
         <v>3.484903528631146E-06</v>
       </c>
-      <c r="D11">
+      <c r="D17">
         <v>5.395992146795605E-05</v>
       </c>
-      <c r="E11">
+      <c r="E17">
         <v>5.334658215079694E-05</v>
       </c>
     </row>

--- a/MinMax/scripts/comparison/violations_comparison_table_118_100.xlsx
+++ b/MinMax/scripts/comparison/violations_comparison_table_118_100.xlsx
@@ -28,7 +28,7 @@
     <t>Vr Vi Model True</t>
   </si>
   <si>
-    <t>Violation Metric</t>
+    <t>Violation Metric [pu]</t>
   </si>
   <si>
     <t>Pg up Avg Violation</t>

--- a/MinMax/scripts/comparison/violations_comparison_table_118_100.xlsx
+++ b/MinMax/scripts/comparison/violations_comparison_table_118_100.xlsx
@@ -459,16 +459,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.0002322860964341089</v>
+        <v>6.411743379430845E-05</v>
       </c>
       <c r="C2">
-        <v>0.000360077916411683</v>
+        <v>0.0002746937971096486</v>
       </c>
       <c r="D2">
-        <v>0.01812904700636864</v>
+        <v>0.01518302876502275</v>
       </c>
       <c r="E2">
-        <v>0.01613542810082436</v>
+        <v>0.01391288638114929</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -476,16 +476,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.08833408355712891</v>
+        <v>0.03057551383972168</v>
       </c>
       <c r="C3">
-        <v>0.117485523223877</v>
+        <v>0.08963537216186523</v>
       </c>
       <c r="D3">
-        <v>0.8357076644897461</v>
+        <v>0.5492148399353027</v>
       </c>
       <c r="E3">
-        <v>0.6218686103820801</v>
+        <v>0.5289676189422607</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -493,16 +493,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>6.460986332967877E-05</v>
+        <v>2.557478364906274E-05</v>
       </c>
       <c r="C4">
-        <v>0.0001794837153283879</v>
+        <v>0.000105529987195041</v>
       </c>
       <c r="D4">
-        <v>0.009775315411388874</v>
+        <v>0.007962608709931374</v>
       </c>
       <c r="E4">
-        <v>0.009787281043827534</v>
+        <v>0.008051705546677113</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -510,16 +510,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.01488589867949486</v>
+        <v>0.01085073407739401</v>
       </c>
       <c r="C5">
-        <v>0.1024265214800835</v>
+        <v>0.03153272345662117</v>
       </c>
       <c r="D5">
-        <v>0.4259120225906372</v>
+        <v>0.207121729850769</v>
       </c>
       <c r="E5">
-        <v>0.2000734806060791</v>
+        <v>0.2201714515686035</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -533,10 +533,10 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0.004053681623190641</v>
+        <v>0.001332205603830516</v>
       </c>
       <c r="E6">
-        <v>0.002465138677507639</v>
+        <v>0.001163617707788944</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -550,10 +550,10 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0.4303729832172394</v>
+        <v>0.1220681369304657</v>
       </c>
       <c r="E7">
-        <v>0.5581697225570679</v>
+        <v>0.07434280216693878</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -567,10 +567,10 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.002058504614979029</v>
+        <v>0.005815492942929268</v>
       </c>
       <c r="E8">
-        <v>0.002076153177767992</v>
+        <v>0.003066015895456076</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -584,10 +584,10 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.1476129293441772</v>
+        <v>0.1879964470863342</v>
       </c>
       <c r="E9">
-        <v>0.1197323873639107</v>
+        <v>0.1501025855541229</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -601,10 +601,10 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>4.741498855764803E-07</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>2.067854802589864E-05</v>
+        <v>2.94799519906519E-06</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -618,10 +618,10 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.004324555397033691</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.01223862171173096</v>
+        <v>0.005012750625610352</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -629,10 +629,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.0001610807958059013</v>
+        <v>0.0001610840845387429</v>
       </c>
       <c r="C12">
-        <v>0.0001610869803698733</v>
+        <v>0.0001610810868442059</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -646,10 +646,10 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.01920199394226074</v>
+        <v>0.01920145750045776</v>
       </c>
       <c r="C13">
-        <v>0.01920586824417114</v>
+        <v>0.0191999077796936</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -663,10 +663,10 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.1711654365062714</v>
+        <v>0.1711650937795639</v>
       </c>
       <c r="C14">
-        <v>0.1711642146110535</v>
+        <v>0.1711640655994415</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -680,10 +680,10 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>8.231096267700195</v>
+        <v>8.231424331665039</v>
       </c>
       <c r="C15">
-        <v>8.231952667236328</v>
+        <v>8.231376647949219</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -697,16 +697,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>6.320630931512637E-08</v>
+        <v>6.159291741150727E-08</v>
       </c>
       <c r="C16">
-        <v>6.146482684925767E-08</v>
+        <v>6.230860885058659E-08</v>
       </c>
       <c r="D16">
-        <v>2.002440429105544E-06</v>
+        <v>1.947465761310281E-06</v>
       </c>
       <c r="E16">
-        <v>1.988179615877243E-06</v>
+        <v>1.990415755967542E-06</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -714,16 +714,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>3.659044569649694E-06</v>
+        <v>3.629340533473812E-06</v>
       </c>
       <c r="C17">
-        <v>3.484903528631146E-06</v>
+        <v>3.110582425500774E-06</v>
       </c>
       <c r="D17">
-        <v>5.395992146795605E-05</v>
+        <v>5.553223611127883E-05</v>
       </c>
       <c r="E17">
-        <v>5.334658215079694E-05</v>
+        <v>5.839782229661983E-05</v>
       </c>
     </row>
   </sheetData>
